--- a/daily_matches/job_matches_2026-10-19.xlsx
+++ b/daily_matches/job_matches_2026-10-19.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,130 +456,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Sr AI/ML Engineer- UHC Tech (Remote)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>The Walt Disney Studios</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Burbank, CA, USA USA</t>
+          <t>Minnetonka, MN, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, LLaMA, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, scikit-learn, FastAPI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a305eedaa5ea3e71</t>
+          <t>https://www.indeed.com/viewjob?jk=187256adb651d30e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Scientist, Modelling &amp; Simulation</t>
+          <t>Solution Architect - Data</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mondelēz International</t>
+          <t>SANTEE COOPER</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>East Hanover, NJ, USA USA</t>
+          <t>Moncks Corner, SC, USA USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, scikit-learn, Git, Matplotlib, Python, R, C++, Julia</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, scikit-learn, Azure ML, Data Lake, MLflow, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1c10c3e3fa6787</t>
+          <t>https://www.indeed.com/viewjob?jk=d0dc4750fd2d1381</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Pipeline Engineer — Apache Airflow (Astronomer) &amp; Python</t>
+          <t>DevOps Machine Learning Infrastructure</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Triade Flevoland</t>
+          <t>Syntiant Corp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Redwood City, CA, USA USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, AKS, Apache Airflow, CI/CD, Git, PySpark, Kafka, Python, SQL</t>
+          <t>RAG, S3, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41823bf35722426c</t>
+          <t>https://www.indeed.com/viewjob?jk=f9b6d2e723c537f7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Remote</t>
+          <t>Databricks Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, USA USA</t>
+          <t>FL, USA USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, S3, Glue, Redshift, MLflow, Snowflake, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -589,147 +589,427 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92800e8ae0ec90fd</t>
+          <t>https://www.indeed.com/viewjob?jk=0b06c504c630d06c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UI Desktop Engineer Hybird, North Carolina Hybrid</t>
+          <t>Databricks Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, USA USA</t>
+          <t>AZ, USA USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, SQL, R, Java, C++, Scala</t>
+          <t>Generative AI, RAG, S3, Glue, Redshift, MLflow, Snowflake, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21f8e27145209897</t>
+          <t>https://www.indeed.com/viewjob?jk=1a7420847497c556</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Embedded Linux Applications Engineer</t>
+          <t>Software Engineer ML Platform</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ammortal Inc</t>
+          <t>Intuitive (Intuitive Surgical)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raleigh, NC, USA USA</t>
+          <t>San Francisco, CA, USA USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Git, Python, R, Java, C++, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, CI/CD, Kafka, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7cbcd2cd1aee590</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb62b181fb4436d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Developer Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Omninode.ai</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, USA USA</t>
+          <t>Research Triangle Park, NC, USA USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LLaMA, Gemini, Docker, CI/CD, Git, Kafka, Python, R, Scala</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Snowflake, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81831a9630d47da0</t>
+          <t>https://www.indeed.com/viewjob?jk=1f3d89fb837011e9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Embedded Linux Applications Engineer</t>
+          <t>Software Engineer – AI and Platform (based in Central or East Coast time zone)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ammortal Inc</t>
+          <t>ColigoMed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Knoxville, TN, USA USA</t>
+          <t>Remote, USA USA</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Docker, Kubernetes, Git, Kafka, PostgreSQL, MongoDB, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4c8d4da122708c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Axiomatic AI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, USA USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61060e733bcb0703</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, USA USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Cortex, Docker, Kubernetes, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bb1d297730e01212</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5bc2c22eb9a1dce</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data &amp; AI Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>FL, USA USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, RAG, MLflow, CI/CD, Terraform, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1371f88e31739c77</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer, Global Banking &amp; Markets, RIA Engineering</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>New York, NY, USA USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Pinecone, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=662b603972838718</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer in Test (SDET), QA - AI Systems</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NEXXA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, USA USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=63ec514f881f6726</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Manufacturing System Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Taylor, TX, USA USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, Git, Python, R, Java, C++, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=66f18423eedcb9b7</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Git, Tableau, Power BI, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac0ce9952102a2ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Postdoctoral Associate, Intelligent Systems Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Virginia Tech</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Blacksburg, VA, USA USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, PyTorch, Python, R, C++, Julia, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f26c5402ddade8f</t>
         </is>
       </c>
     </row>
